--- a/assessment/data/SC13_2025assessmentInputData_V3.xlsx
+++ b/assessment/data/SC13_2025assessmentInputData_V3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leeqi/Library/CloudStorage/GoogleDrive-leeqi@uw.edu/My Drive/SPRFMO/jjm/assessment/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32AEB7E2-A1DE-B74A-9CC6-02B350A2E1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A345C135-246D-3B45-848A-51C1F42B6505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15120" yWindow="760" windowWidth="15120" windowHeight="18880" activeTab="3" xr2:uid="{11C67D07-EBA6-4D97-A3E6-A5FACAECFD42}"/>
+    <workbookView xWindow="15120" yWindow="760" windowWidth="15120" windowHeight="18880" activeTab="4" xr2:uid="{11C67D07-EBA6-4D97-A3E6-A5FACAECFD42}"/>
   </bookViews>
   <sheets>
     <sheet name="ageComps" sheetId="1" r:id="rId1"/>
@@ -4320,8 +4320,8 @@
         <v>1068425.3710330399</v>
       </c>
       <c r="D3" s="3">
-        <f>75+208</f>
-        <v>283</v>
+        <f>75+208000</f>
+        <v>208075</v>
       </c>
       <c r="E3" s="1">
         <v>11055.456022689201</v>
@@ -4757,12 +4757,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4771,7 +4765,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100812D0B056278C642B7C89719D0EEC9C4" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="53e5abc0267b36fb4b4009f6291778a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f419981a-ca0a-4e56-9512-575f16b7ea2d" xmlns:ns3="5ce05999-5605-4258-98fc-62ff4522b5fb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2d299d2548571e9774994fb9c4dbbeb8" ns2:_="" ns3:_="">
     <xsd:import namespace="f419981a-ca0a-4e56-9512-575f16b7ea2d"/>
@@ -4986,16 +4980,13 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2AFB9C7-A01A-423B-A442-B6889BA2E519}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228CE105-4287-40ED-B72B-E33A77B67D61}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -5003,7 +4994,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFE542F3-5C46-43FB-860A-90AC96253C26}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5020,4 +5011,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2AFB9C7-A01A-423B-A442-B6889BA2E519}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/assessment/data/SC13_2025assessmentInputData_V3.xlsx
+++ b/assessment/data/SC13_2025assessmentInputData_V3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leeqi/Library/CloudStorage/GoogleDrive-leeqi@uw.edu/My Drive/SPRFMO/jjm/assessment/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A345C135-246D-3B45-848A-51C1F42B6505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C770C97F-E524-9743-928D-32084D612FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15120" yWindow="760" windowWidth="15120" windowHeight="18880" activeTab="4" xr2:uid="{11C67D07-EBA6-4D97-A3E6-A5FACAECFD42}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Catch" sheetId="6" r:id="rId5"/>
     <sheet name="Acoustic" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -84,7 +84,7 @@
     <numFmt numFmtId="164" formatCode="##.\ ###"/>
     <numFmt numFmtId="165" formatCode="###\ ###\ ###"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,6 +110,11 @@
       <color indexed="18"/>
       <name val="Geneva"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
     </font>
   </fonts>
   <fills count="3">
@@ -139,7 +144,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -151,6 +156,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4327,6 +4333,10 @@
         <v>11055.456022689201</v>
       </c>
     </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+    </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="I15" s="5"/>
     </row>
@@ -4757,15 +4767,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100812D0B056278C642B7C89719D0EEC9C4" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="53e5abc0267b36fb4b4009f6291778a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f419981a-ca0a-4e56-9512-575f16b7ea2d" xmlns:ns3="5ce05999-5605-4258-98fc-62ff4522b5fb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2d299d2548571e9774994fb9c4dbbeb8" ns2:_="" ns3:_="">
     <xsd:import namespace="f419981a-ca0a-4e56-9512-575f16b7ea2d"/>
@@ -4980,6 +4981,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -4987,14 +4997,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228CE105-4287-40ED-B72B-E33A77B67D61}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFE542F3-5C46-43FB-860A-90AC96253C26}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5013,6 +5015,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228CE105-4287-40ED-B72B-E33A77B67D61}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2AFB9C7-A01A-423B-A442-B6889BA2E519}">
   <ds:schemaRefs>

--- a/assessment/data/SC13_2025assessmentInputData_V3.xlsx
+++ b/assessment/data/SC13_2025assessmentInputData_V3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leeqi/Library/CloudStorage/GoogleDrive-leeqi@uw.edu/My Drive/SPRFMO/jjm/assessment/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C770C97F-E524-9743-928D-32084D612FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2090BE10-30DF-6F4A-AA92-D9B9CF835594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15120" yWindow="760" windowWidth="15120" windowHeight="18880" activeTab="4" xr2:uid="{11C67D07-EBA6-4D97-A3E6-A5FACAECFD42}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="Catch" sheetId="6" r:id="rId5"/>
     <sheet name="Acoustic" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191028" calcOnSave="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -84,7 +84,7 @@
     <numFmt numFmtId="164" formatCode="##.\ ###"/>
     <numFmt numFmtId="165" formatCode="###\ ###\ ###"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,11 +110,6 @@
       <color indexed="18"/>
       <name val="Geneva"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos"/>
     </font>
   </fonts>
   <fills count="3">
@@ -144,7 +139,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -155,8 +150,7 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4273,13 +4267,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA686FE5-9B92-4435-B67D-4EE55A2A4B01}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="9" max="9" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4296,26 +4291,26 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2024</v>
       </c>
-      <c r="B2" s="3">
-        <v>105023.27694197861</v>
-      </c>
-      <c r="C2" s="3">
-        <v>974394.19195802161</v>
+      <c r="B2" s="5">
+        <v>105308.75252952188</v>
+      </c>
+      <c r="C2" s="5">
+        <v>977040.24747047806</v>
       </c>
       <c r="D2" s="3">
-        <f>181838.846+55.65</f>
-        <v>181894.49599999998</v>
+        <f>217212+30</f>
+        <v>217242</v>
       </c>
       <c r="E2" s="3">
-        <f>17773.871+1796.87+15857.084</f>
-        <v>35427.824999999997</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <f>30479</f>
+        <v>30479</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2025</v>
       </c>
@@ -4330,15 +4325,9 @@
         <v>208075</v>
       </c>
       <c r="E3" s="1">
-        <v>11055.456022689201</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I15" s="5"/>
+        <f>11055+2508</f>
+        <v>13563</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4767,6 +4756,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100812D0B056278C642B7C89719D0EEC9C4" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="53e5abc0267b36fb4b4009f6291778a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f419981a-ca0a-4e56-9512-575f16b7ea2d" xmlns:ns3="5ce05999-5605-4258-98fc-62ff4522b5fb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2d299d2548571e9774994fb9c4dbbeb8" ns2:_="" ns3:_="">
     <xsd:import namespace="f419981a-ca0a-4e56-9512-575f16b7ea2d"/>
@@ -4981,22 +4985,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2AFB9C7-A01A-423B-A442-B6889BA2E519}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228CE105-4287-40ED-B72B-E33A77B67D61}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFE542F3-5C46-43FB-860A-90AC96253C26}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5013,21 +5019,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{228CE105-4287-40ED-B72B-E33A77B67D61}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2AFB9C7-A01A-423B-A442-B6889BA2E519}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>